--- a/artfynd/A 25608-2026 artfynd.xlsx
+++ b/artfynd/A 25608-2026 artfynd.xlsx
@@ -3116,7 +3116,7 @@
         <v>133925242</v>
       </c>
       <c r="B24" t="n">
-        <v>91981</v>
+        <v>91988</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 25608-2026 artfynd.xlsx
+++ b/artfynd/A 25608-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AY25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>16885667</v>
+        <v>16885666</v>
       </c>
       <c r="B2" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>1100 m S Tellejåkk, Lu lm</t>
+          <t>1200 m S Tellejåkk, Lu lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>720125.9858455057</v>
+        <v>720077</v>
       </c>
       <c r="R2" t="n">
-        <v>7334106.159908929</v>
+        <v>7333978</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2014-08-18</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2014-08-18</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -792,15 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>16885666</v>
+        <v>80984495</v>
       </c>
       <c r="B3" t="n">
-        <v>77177</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -828,14 +808,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>1200 m S Tellejåkk, Lu lm</t>
+          <t>Pärlskalbäcken, Lu lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>720077.1478254406</v>
+        <v>720110</v>
       </c>
       <c r="R3" t="n">
-        <v>7333977.94358702</v>
+        <v>7334046</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,27 +842,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2014-08-18</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-08-11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2014-08-18</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Sveaskog naturvärdesinventering, inventerare: Rasmus Häggqvist</t>
+          <t>2019-08-11</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,49 +862,44 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Caspar Ström</t>
+          <t>Sture Westerberg</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Sveaskog genom Johan Ekenstedt</t>
+          <t>Helena Björnström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>80984503</v>
+        <v>80984496</v>
       </c>
       <c r="B4" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -949,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>720316.1110166652</v>
+        <v>719834</v>
       </c>
       <c r="R4" t="n">
-        <v>7334160.927699802</v>
+        <v>7334183</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,19 +942,9 @@
           <t>2019-08-11</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2019-08-11</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,15 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>80984480</v>
+        <v>80984487</v>
       </c>
       <c r="B5" t="n">
-        <v>90657</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92083</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1037,21 +982,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4365</v>
+        <v>1503</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1061,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>720093.1649854479</v>
+        <v>719823</v>
       </c>
       <c r="R5" t="n">
-        <v>7334024.061883006</v>
+        <v>7334170</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1094,19 +1039,9 @@
           <t>2019-08-11</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2019-08-11</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,15 +1068,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>80984484</v>
+        <v>80984497</v>
       </c>
       <c r="B6" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1149,21 +1079,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1173,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>720042.0728595126</v>
+        <v>719812</v>
       </c>
       <c r="R6" t="n">
-        <v>7334029.88029587</v>
+        <v>7334171</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1206,19 +1136,9 @@
           <t>2019-08-11</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2019-08-11</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1245,15 +1165,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>80984496</v>
+        <v>80984502</v>
       </c>
       <c r="B7" t="n">
-        <v>77177</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1261,21 +1176,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1285,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>719834.156779814</v>
+        <v>720322</v>
       </c>
       <c r="R7" t="n">
-        <v>7334183.011565209</v>
+        <v>7334224</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1318,19 +1233,9 @@
           <t>2019-08-11</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2019-08-11</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1357,37 +1262,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>80984481</v>
+        <v>80984503</v>
       </c>
       <c r="B8" t="n">
-        <v>78503</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6456</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1397,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>720052.2065921692</v>
+        <v>720316</v>
       </c>
       <c r="R8" t="n">
-        <v>7334093.896721153</v>
+        <v>7334161</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1430,19 +1330,9 @@
           <t>2019-08-11</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2019-08-11</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1469,15 +1359,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>80984470</v>
+        <v>80984505</v>
       </c>
       <c r="B9" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1485,21 +1370,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1509,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>719860.1629516791</v>
+        <v>720321</v>
       </c>
       <c r="R9" t="n">
-        <v>7334189.926282424</v>
+        <v>7334098</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1542,19 +1427,9 @@
           <t>2019-08-11</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2019-08-11</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1584,12 +1459,7 @@
         <v>80984479</v>
       </c>
       <c r="B10" t="n">
-        <v>90657</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93201</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1621,10 +1491,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>720115.9720220829</v>
+        <v>720116</v>
       </c>
       <c r="R10" t="n">
-        <v>7334051.127007321</v>
+        <v>7334051</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1654,19 +1524,9 @@
           <t>2019-08-11</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2019-08-11</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1693,37 +1553,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>80984497</v>
+        <v>80984480</v>
       </c>
       <c r="B11" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93201</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>4365</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1733,10 +1588,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>719811.8071051834</v>
+        <v>720093</v>
       </c>
       <c r="R11" t="n">
-        <v>7334171.078264887</v>
+        <v>7334024</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1766,19 +1621,9 @@
           <t>2019-08-11</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2019-08-11</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1805,15 +1650,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>80984490</v>
+        <v>129000486</v>
       </c>
       <c r="B12" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1821,34 +1661,38 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>4366</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Pärlskalbäcken, Lu lm</t>
+          <t>Tellejåkk, Lu lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>719771.880424383</v>
+        <v>720161</v>
       </c>
       <c r="R12" t="n">
-        <v>7334154.109205235</v>
+        <v>7334167</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1875,22 +1719,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2019-08-11</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2019-08-11</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1905,62 +1744,61 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Sture Westerberg</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>80984505</v>
+        <v>129000487</v>
       </c>
       <c r="B13" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Pärlskalbäcken, Lu lm</t>
+          <t>Tellejåkk, Lu lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>720321.0026368516</v>
+        <v>720349</v>
       </c>
       <c r="R13" t="n">
-        <v>7334098.080209779</v>
+        <v>7334152</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1987,22 +1825,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2019-08-11</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2019-08-11</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2017,27 +1850,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Sture Westerberg</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>80984495</v>
+        <v>129000489</v>
       </c>
       <c r="B14" t="n">
-        <v>77177</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2045,34 +1873,38 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>353</v>
+        <v>4366</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Pärlskalbäcken, Lu lm</t>
+          <t>Tellejåkk, Lu lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>720109.8239775114</v>
+        <v>720534</v>
       </c>
       <c r="R14" t="n">
-        <v>7334046.161713282</v>
+        <v>7334112</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2099,22 +1931,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2019-08-11</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2019-08-11</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2129,27 +1956,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Sture Westerberg</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>80984477</v>
+        <v>16885667</v>
       </c>
       <c r="B15" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2177,14 +1999,14 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Pärlskalbäcken, Lu lm</t>
+          <t>1100 m S Tellejåkk, Lu lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>720041.1158399449</v>
+        <v>720126</v>
       </c>
       <c r="R15" t="n">
-        <v>7334057.953030611</v>
+        <v>7334106</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2211,22 +2033,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2019-08-11</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-08-18</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2019-08-11</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-08-18</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Sveaskog naturvärdesinventering, inventerare: Rasmus Häggqvist</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2241,49 +2058,44 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Sture Westerberg</t>
+          <t>Caspar Ström</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Sveaskog genom Johan Ekenstedt</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>80984487</v>
+        <v>80984477</v>
       </c>
       <c r="B16" t="n">
-        <v>89545</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1503</v>
+        <v>5442</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2293,10 +2105,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>719822.9241371683</v>
+        <v>720041</v>
       </c>
       <c r="R16" t="n">
-        <v>7334169.902057269</v>
+        <v>7334058</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2326,19 +2138,9 @@
           <t>2019-08-11</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2019-08-11</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2365,53 +2167,52 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>80984502</v>
+        <v>133925242</v>
       </c>
       <c r="B17" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91995</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>5442</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Pärlskalbäcken, Lu lm</t>
+          <t>Tellejåkk, Lu lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>720321.8045566493</v>
+        <v>720043</v>
       </c>
       <c r="R17" t="n">
-        <v>7334224.189779983</v>
+        <v>7333956</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2435,22 +2236,27 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2019-08-11</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2019-08-11</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>09:46</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2465,61 +2271,57 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Sture Westerberg</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129000491</v>
+        <v>80984490</v>
       </c>
       <c r="B18" t="n">
-        <v>78801</v>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Tellejåkk, Lu lm</t>
+          <t>Pärlskalbäcken, Lu lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>720506</v>
+        <v>719772</v>
       </c>
       <c r="R18" t="n">
-        <v>7334145</v>
+        <v>7334154</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2546,17 +2348,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2019-08-11</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2019-08-11</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2571,22 +2368,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Sture Westerberg</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Helena Björnström</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129000485</v>
+        <v>80984491</v>
       </c>
       <c r="B19" t="n">
-        <v>92866</v>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2594,38 +2391,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>232140</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Tellejåkk, Lu lm</t>
+          <t>Pärlskalbäcken, Lu lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>720125</v>
+        <v>720366</v>
       </c>
       <c r="R19" t="n">
-        <v>7334096</v>
+        <v>7334007</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2652,17 +2445,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2019-08-11</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2019-08-11</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2677,44 +2465,44 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Sture Westerberg</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Helena Björnström</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129000486</v>
+        <v>129000491</v>
       </c>
       <c r="B20" t="n">
-        <v>92847</v>
+        <v>79084</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4366</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2728,10 +2516,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>720161</v>
+        <v>720506</v>
       </c>
       <c r="R20" t="n">
-        <v>7334167</v>
+        <v>7334145</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2795,49 +2583,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129000484</v>
+        <v>80984470</v>
       </c>
       <c r="B21" t="n">
-        <v>92866</v>
+        <v>79946</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>232140</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Tellejåkk, Lu lm</t>
+          <t>Pärlskalbäcken, Lu lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>719825</v>
+        <v>719860</v>
       </c>
       <c r="R21" t="n">
-        <v>7334177</v>
+        <v>7334190</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2864,17 +2648,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2019-08-11</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2019-08-11</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2889,22 +2668,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Sture Westerberg</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Helena Björnström</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129000487</v>
+        <v>80984481</v>
       </c>
       <c r="B22" t="n">
-        <v>92847</v>
+        <v>80336</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2912,38 +2691,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4366</v>
+        <v>6456</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Tellejåkk, Lu lm</t>
+          <t>Pärlskalbäcken, Lu lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>720349</v>
+        <v>720052</v>
       </c>
       <c r="R22" t="n">
-        <v>7334152</v>
+        <v>7334094</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2970,17 +2745,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2019-08-11</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2019-08-11</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2995,61 +2765,57 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Sture Westerberg</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Helena Björnström</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129000489</v>
+        <v>80984484</v>
       </c>
       <c r="B23" t="n">
-        <v>92847</v>
+        <v>79085</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4366</v>
+        <v>228912</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Tellejåkk, Lu lm</t>
+          <t>Pärlskalbäcken, Lu lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>720534</v>
+        <v>720042</v>
       </c>
       <c r="R23" t="n">
-        <v>7334112</v>
+        <v>7334030</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3076,17 +2842,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2019-08-11</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2019-08-11</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3101,44 +2862,44 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Sture Westerberg</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Helena Björnström</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133925242</v>
+        <v>129000484</v>
       </c>
       <c r="B24" t="n">
-        <v>91988</v>
+        <v>93228</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5442</v>
+        <v>232140</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Niemelä &amp; Kinnunen</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3152,13 +2913,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>720043</v>
+        <v>719825</v>
       </c>
       <c r="R24" t="n">
-        <v>7333956</v>
+        <v>7334177</v>
       </c>
       <c r="S24" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3182,22 +2943,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>09:46</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>09:46</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -3226,6 +2977,112 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>129000485</v>
+      </c>
+      <c r="B25" t="n">
+        <v>93228</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>232140</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Tajgataggsvamp</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Phellodon secretus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Niemelä &amp; Kinnunen</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Tellejåkk, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>720125</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7334096</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 25608-2026 artfynd.xlsx
+++ b/artfynd/A 25608-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AY70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>16885666</v>
+        <v>135504188</v>
       </c>
       <c r="B2" t="n">
-        <v>78993</v>
+        <v>83350</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>353</v>
+        <v>308</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>1200 m S Tellejåkk, Lu lm</t>
+          <t>Tellejokk, Lu lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>720077</v>
+        <v>719995</v>
       </c>
       <c r="R2" t="n">
-        <v>7333978</v>
+        <v>7334207</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -740,17 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2014-08-18</t>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2014-08-18</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Sveaskog naturvärdesinventering, inventerare: Rasmus Häggqvist</t>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,19 +770,19 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Caspar Ström</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Sveaskog genom Johan Ekenstedt</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>80984495</v>
+        <v>16885666</v>
       </c>
       <c r="B3" t="n">
         <v>78993</v>
@@ -808,14 +813,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Pärlskalbäcken, Lu lm</t>
+          <t>1200 m S Tellejåkk, Lu lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>720110</v>
+        <v>720077</v>
       </c>
       <c r="R3" t="n">
-        <v>7334046</v>
+        <v>7333978</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -842,12 +847,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2019-08-11</t>
+          <t>2014-08-18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2019-08-11</t>
+          <t>2014-08-18</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Sveaskog naturvärdesinventering, inventerare: Rasmus Häggqvist</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -862,19 +872,19 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Sture Westerberg</t>
+          <t>Caspar Ström</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Sveaskog genom Johan Ekenstedt</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>80984496</v>
+        <v>80984495</v>
       </c>
       <c r="B4" t="n">
         <v>78993</v>
@@ -909,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>719834</v>
+        <v>720110</v>
       </c>
       <c r="R4" t="n">
-        <v>7334183</v>
+        <v>7334046</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -971,32 +981,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>80984487</v>
+        <v>80984496</v>
       </c>
       <c r="B5" t="n">
-        <v>92083</v>
+        <v>78993</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1503</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>719823</v>
+        <v>719834</v>
       </c>
       <c r="R5" t="n">
-        <v>7334170</v>
+        <v>7334183</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1068,10 +1078,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>80984497</v>
+        <v>135504199</v>
       </c>
       <c r="B6" t="n">
-        <v>93197</v>
+        <v>79039</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1079,37 +1089,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Pärlskalbäcken, Lu lm</t>
+          <t>Tellejokk, Lu lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>719812</v>
+        <v>720174</v>
       </c>
       <c r="R6" t="n">
-        <v>7334171</v>
+        <v>7333975</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1133,12 +1143,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2019-08-11</t>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2019-08-11</t>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1153,22 +1173,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Sture Westerberg</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>80984502</v>
+        <v>135504204</v>
       </c>
       <c r="B7" t="n">
-        <v>93197</v>
+        <v>79039</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1176,37 +1196,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Pärlskalbäcken, Lu lm</t>
+          <t>Tellejåkk, Lu lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>720322</v>
+        <v>719841</v>
       </c>
       <c r="R7" t="n">
-        <v>7334224</v>
+        <v>7334205</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1230,12 +1250,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2019-08-11</t>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2019-08-11</t>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1250,44 +1280,44 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Sture Westerberg</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>80984503</v>
+        <v>80984487</v>
       </c>
       <c r="B8" t="n">
-        <v>93197</v>
+        <v>92083</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>1503</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>720316</v>
+        <v>719823</v>
       </c>
       <c r="R8" t="n">
-        <v>7334161</v>
+        <v>7334170</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1359,48 +1389,48 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>80984505</v>
+        <v>135504206</v>
       </c>
       <c r="B9" t="n">
-        <v>93197</v>
+        <v>92153</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>1503</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Pärlskalbäcken, Lu lm</t>
+          <t>Tellejåkk, Lu lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>720321</v>
+        <v>719795</v>
       </c>
       <c r="R9" t="n">
-        <v>7334098</v>
+        <v>7334134</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1424,12 +1454,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2019-08-11</t>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2019-08-11</t>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1444,22 +1484,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Sture Westerberg</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>80984479</v>
+        <v>135504226</v>
       </c>
       <c r="B10" t="n">
-        <v>93201</v>
+        <v>92153</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1467,37 +1507,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4365</v>
+        <v>1503</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Pärlskalbäcken, Lu lm</t>
+          <t>Tellejåkk, Lu lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>720116</v>
+        <v>720053</v>
       </c>
       <c r="R10" t="n">
-        <v>7334051</v>
+        <v>7334194</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1521,12 +1561,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2019-08-11</t>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2019-08-11</t>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1541,22 +1591,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Sture Westerberg</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>80984480</v>
+        <v>135504228</v>
       </c>
       <c r="B11" t="n">
-        <v>93201</v>
+        <v>92153</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1564,37 +1614,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4365</v>
+        <v>1503</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Pärlskalbäcken, Lu lm</t>
+          <t>Tellejåkk, Lu lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>720093</v>
+        <v>720162</v>
       </c>
       <c r="R11" t="n">
-        <v>7334024</v>
+        <v>7334159</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1618,12 +1668,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2019-08-11</t>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2019-08-11</t>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1638,22 +1698,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Sture Westerberg</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129000486</v>
+        <v>135504177</v>
       </c>
       <c r="B12" t="n">
-        <v>93209</v>
+        <v>90997</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1661,41 +1721,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4366</v>
+        <v>1962</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Tellejåkk, Lu lm</t>
+          <t>Tellejokk, Lu lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>720161</v>
+        <v>719793</v>
       </c>
       <c r="R12" t="n">
-        <v>7334167</v>
+        <v>7334135</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1719,17 +1775,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1744,22 +1805,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129000487</v>
+        <v>135504187</v>
       </c>
       <c r="B13" t="n">
-        <v>93209</v>
+        <v>90997</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1767,41 +1828,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4366</v>
+        <v>1962</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Tellejåkk, Lu lm</t>
+          <t>Tellejokk, Lu lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>720349</v>
+        <v>719933</v>
       </c>
       <c r="R13" t="n">
-        <v>7334152</v>
+        <v>7334218</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1825,17 +1882,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1850,22 +1912,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129000489</v>
+        <v>135504207</v>
       </c>
       <c r="B14" t="n">
-        <v>93209</v>
+        <v>92027</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1873,41 +1935,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4366</v>
+        <v>2079</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(S.Lundell) Parmasto</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Tellejåkk, Lu lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>720534</v>
+        <v>719794</v>
       </c>
       <c r="R14" t="n">
-        <v>7334112</v>
+        <v>7334139</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1931,17 +1989,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1956,22 +2019,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>16885667</v>
+        <v>135504220</v>
       </c>
       <c r="B15" t="n">
-        <v>91930</v>
+        <v>92027</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1979,37 +2042,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5442</v>
+        <v>2079</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>1100 m S Tellejåkk, Lu lm</t>
+          <t>Tellejåkk, Lu lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>720126</v>
+        <v>719978</v>
       </c>
       <c r="R15" t="n">
-        <v>7334106</v>
+        <v>7334223</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2033,17 +2096,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2014-08-18</t>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2014-08-18</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Sveaskog naturvärdesinventering, inventerare: Rasmus Häggqvist</t>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2058,22 +2126,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Caspar Ström</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Sveaskog genom Johan Ekenstedt</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>80984477</v>
+        <v>135504222</v>
       </c>
       <c r="B16" t="n">
-        <v>91930</v>
+        <v>92027</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2081,37 +2149,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5442</v>
+        <v>2079</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Pärlskalbäcken, Lu lm</t>
+          <t>Tellejåkk, Lu lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>720041</v>
+        <v>719990</v>
       </c>
       <c r="R16" t="n">
-        <v>7334058</v>
+        <v>7334243</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2135,12 +2203,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2019-08-11</t>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2019-08-11</t>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2155,22 +2233,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Sture Westerberg</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133925242</v>
+        <v>135504232</v>
       </c>
       <c r="B17" t="n">
-        <v>91995</v>
+        <v>92027</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2178,41 +2256,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5442</v>
+        <v>2079</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(S.Lundell) Parmasto</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Tellejåkk, Lu lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>720043</v>
+        <v>720167</v>
       </c>
       <c r="R17" t="n">
-        <v>7333956</v>
+        <v>7334013</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2236,27 +2310,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:46</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2271,60 +2340,60 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>80984490</v>
+        <v>135504223</v>
       </c>
       <c r="B18" t="n">
-        <v>79327</v>
+        <v>91896</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>3242</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Pärlskalbäcken, Lu lm</t>
+          <t>Tellejåkk, Lu lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>719772</v>
+        <v>720026</v>
       </c>
       <c r="R18" t="n">
-        <v>7334154</v>
+        <v>7334208</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2348,12 +2417,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2019-08-11</t>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2019-08-11</t>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2368,60 +2447,60 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Sture Westerberg</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>80984491</v>
+        <v>135504227</v>
       </c>
       <c r="B19" t="n">
-        <v>79327</v>
+        <v>91896</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>3242</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Pärlskalbäcken, Lu lm</t>
+          <t>Tellejåkk, Lu lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>720366</v>
+        <v>720066</v>
       </c>
       <c r="R19" t="n">
-        <v>7334007</v>
+        <v>7334187</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2445,12 +2524,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2019-08-11</t>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2019-08-11</t>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2465,22 +2554,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Sture Westerberg</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129000491</v>
+        <v>135504229</v>
       </c>
       <c r="B20" t="n">
-        <v>79084</v>
+        <v>91896</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2488,41 +2577,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>3242</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Tellejåkk, Lu lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>720506</v>
+        <v>720160</v>
       </c>
       <c r="R20" t="n">
-        <v>7334145</v>
+        <v>7334058</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2546,17 +2631,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2571,22 +2661,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>80984470</v>
+        <v>135504236</v>
       </c>
       <c r="B21" t="n">
-        <v>79946</v>
+        <v>93263</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2594,37 +2684,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>4361</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Pärlskalbäcken, Lu lm</t>
+          <t>Tellejåkk, Lu lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>719860</v>
+        <v>720151</v>
       </c>
       <c r="R21" t="n">
-        <v>7334190</v>
+        <v>7334030</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2648,12 +2738,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2019-08-11</t>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2019-08-11</t>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2668,44 +2768,44 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Sture Westerberg</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>80984481</v>
+        <v>80984497</v>
       </c>
       <c r="B22" t="n">
-        <v>80336</v>
+        <v>93197</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6456</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2715,10 +2815,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>720052</v>
+        <v>719812</v>
       </c>
       <c r="R22" t="n">
-        <v>7334094</v>
+        <v>7334171</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2777,10 +2877,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>80984484</v>
+        <v>80984502</v>
       </c>
       <c r="B23" t="n">
-        <v>79085</v>
+        <v>93197</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2788,21 +2888,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2812,10 +2912,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>720042</v>
+        <v>720322</v>
       </c>
       <c r="R23" t="n">
-        <v>7334030</v>
+        <v>7334224</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2874,49 +2974,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129000484</v>
+        <v>80984503</v>
       </c>
       <c r="B24" t="n">
-        <v>93228</v>
+        <v>93197</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>232140</v>
+        <v>4364</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Tellejåkk, Lu lm</t>
+          <t>Pärlskalbäcken, Lu lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>719825</v>
+        <v>720316</v>
       </c>
       <c r="R24" t="n">
-        <v>7334177</v>
+        <v>7334161</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2943,17 +3039,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2019-08-11</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2019-08-11</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2968,61 +3059,57 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Sture Westerberg</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Helena Björnström</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129000485</v>
+        <v>80984505</v>
       </c>
       <c r="B25" t="n">
-        <v>93228</v>
+        <v>93197</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>232140</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Tellejåkk, Lu lm</t>
+          <t>Pärlskalbäcken, Lu lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>720125</v>
+        <v>720321</v>
       </c>
       <c r="R25" t="n">
-        <v>7334096</v>
+        <v>7334098</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3049,17 +3136,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2019-08-11</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2019-08-11</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3074,15 +3156,4762 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
+          <t>Sture Westerberg</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>135504181</v>
+      </c>
+      <c r="B26" t="n">
+        <v>93271</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Tellejokk, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>719937</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7334093</v>
+      </c>
+      <c r="S26" t="n">
+        <v>6</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>12:36</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>12:36</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>135504182</v>
+      </c>
+      <c r="B27" t="n">
+        <v>93271</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Tellejokk, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>719942</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7334096</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>135504184</v>
+      </c>
+      <c r="B28" t="n">
+        <v>93271</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Tellejokk, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>719948</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7334156</v>
+      </c>
+      <c r="S28" t="n">
+        <v>6</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>135504185</v>
+      </c>
+      <c r="B29" t="n">
+        <v>93271</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Tellejokk, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>719927</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7334199</v>
+      </c>
+      <c r="S29" t="n">
+        <v>6</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>13:47</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>13:47</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>135504191</v>
+      </c>
+      <c r="B30" t="n">
+        <v>93271</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Tellejokk, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>719999</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7334211</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>15:32</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>15:32</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>135504194</v>
+      </c>
+      <c r="B31" t="n">
+        <v>93271</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Tellejokk, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>720094</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7334186</v>
+      </c>
+      <c r="S31" t="n">
+        <v>6</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>135504209</v>
+      </c>
+      <c r="B32" t="n">
+        <v>93271</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Tellejåkk, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>719848</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7334077</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>12:16</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>12:16</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>135504211</v>
+      </c>
+      <c r="B33" t="n">
+        <v>93271</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Tellejåkk, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>719865</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7334082</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>12:27</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>12:27</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>135504219</v>
+      </c>
+      <c r="B34" t="n">
+        <v>93271</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Tellejåkk, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>719953</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7334191</v>
+      </c>
+      <c r="S34" t="n">
+        <v>9</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>13:48</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>13:48</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>80984479</v>
+      </c>
+      <c r="B35" t="n">
+        <v>93201</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>4365</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Smalfotad taggsvamp</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Hydnellum gracilipes</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Pärlskalbäcken, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>720116</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7334051</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2019-08-11</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2019-08-11</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Sture Westerberg</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>80984480</v>
+      </c>
+      <c r="B36" t="n">
+        <v>93201</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>4365</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Smalfotad taggsvamp</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Hydnellum gracilipes</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Pärlskalbäcken, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>720093</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7334024</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2019-08-11</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2019-08-11</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Sture Westerberg</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>129000486</v>
+      </c>
+      <c r="B37" t="n">
+        <v>93209</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Tellejåkk, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>720161</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7334167</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
           <t>Mimmi Persson</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
+      <c r="AX37" t="inlineStr">
         <is>
           <t>Mimmi Persson</t>
         </is>
       </c>
-      <c r="AY25" t="inlineStr"/>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>129000487</v>
+      </c>
+      <c r="B38" t="n">
+        <v>93209</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Tellejåkk, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>720349</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7334152</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>129000489</v>
+      </c>
+      <c r="B39" t="n">
+        <v>93209</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Tellejåkk, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>720534</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7334112</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>16885667</v>
+      </c>
+      <c r="B40" t="n">
+        <v>91930</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>1100 m S Tellejåkk, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>720126</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7334106</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2014-08-18</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2014-08-18</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Sveaskog naturvärdesinventering, inventerare: Rasmus Häggqvist</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Sveaskog genom Johan Ekenstedt</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>80984477</v>
+      </c>
+      <c r="B41" t="n">
+        <v>91930</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Pärlskalbäcken, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>720041</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7334058</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2019-08-11</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2019-08-11</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Sture Westerberg</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>133925242</v>
+      </c>
+      <c r="B42" t="n">
+        <v>91995</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Tellejåkk, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>720043</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7333956</v>
+      </c>
+      <c r="S42" t="n">
+        <v>25</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>09:46</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>09:46</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>135504198</v>
+      </c>
+      <c r="B43" t="n">
+        <v>93255</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>6055</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Spadskinn</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Stereopsis vitellina</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(S.Lundell) D.A.Reid</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Tellejokk, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>720172</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7333985</v>
+      </c>
+      <c r="S43" t="n">
+        <v>6</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>16:23</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>16:23</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>80984490</v>
+      </c>
+      <c r="B44" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Pärlskalbäcken, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>719772</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7334154</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2019-08-11</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2019-08-11</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Sture Westerberg</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>80984491</v>
+      </c>
+      <c r="B45" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Pärlskalbäcken, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>720366</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7334007</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2019-08-11</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2019-08-11</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Sture Westerberg</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>135504200</v>
+      </c>
+      <c r="B46" t="n">
+        <v>78776</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Tellejokk, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>720190</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7333962</v>
+      </c>
+      <c r="S46" t="n">
+        <v>5</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>16:33</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>16:33</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>129000491</v>
+      </c>
+      <c r="B47" t="n">
+        <v>79084</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Tellejåkk, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>720506</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7334145</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>135504214</v>
+      </c>
+      <c r="B48" t="n">
+        <v>79130</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Tellejåkk, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>719950</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7334140</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>135504235</v>
+      </c>
+      <c r="B49" t="n">
+        <v>79130</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Tellejåkk, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>720195</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7333954</v>
+      </c>
+      <c r="S49" t="n">
+        <v>5</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>16:34</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>16:34</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>80984470</v>
+      </c>
+      <c r="B50" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Pärlskalbäcken, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>719860</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7334190</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2019-08-11</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2019-08-11</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Sture Westerberg</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>80984481</v>
+      </c>
+      <c r="B51" t="n">
+        <v>80336</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Pärlskalbäcken, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>720052</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7334094</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2019-08-11</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2019-08-11</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Sture Westerberg</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>135504190</v>
+      </c>
+      <c r="B52" t="n">
+        <v>78377</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>6487</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Blågrå svartspik</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis fennica</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Tellejokk, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>720004</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7334229</v>
+      </c>
+      <c r="S52" t="n">
+        <v>5</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>135504192</v>
+      </c>
+      <c r="B53" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Tellejokk, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>720018</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7334206</v>
+      </c>
+      <c r="S53" t="n">
+        <v>5</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Spillning</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>135504212</v>
+      </c>
+      <c r="B54" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Tellejåkk, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>719954</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7334093</v>
+      </c>
+      <c r="S54" t="n">
+        <v>8</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Spillning</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>135504205</v>
+      </c>
+      <c r="B55" t="n">
+        <v>98066</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Tellejåkk, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>719826</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7334115</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>135504197</v>
+      </c>
+      <c r="B56" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Tellejokk, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>720196</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7334052</v>
+      </c>
+      <c r="S56" t="n">
+        <v>5</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>16:09</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>16:09</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>80984484</v>
+      </c>
+      <c r="B57" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Pärlskalbäcken, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>720042</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7334030</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2019-08-11</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2019-08-11</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Sture Westerberg</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>135504183</v>
+      </c>
+      <c r="B58" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Tellejokk, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>719960</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7334135</v>
+      </c>
+      <c r="S58" t="n">
+        <v>5</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>135504189</v>
+      </c>
+      <c r="B59" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Tellejokk, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>719990</v>
+      </c>
+      <c r="R59" t="n">
+        <v>7334219</v>
+      </c>
+      <c r="S59" t="n">
+        <v>5</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>135504193</v>
+      </c>
+      <c r="B60" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Tellejokk, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>720034</v>
+      </c>
+      <c r="R60" t="n">
+        <v>7334183</v>
+      </c>
+      <c r="S60" t="n">
+        <v>6</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>15:41</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>15:41</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>135504201</v>
+      </c>
+      <c r="B61" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Tellejokk, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>720188</v>
+      </c>
+      <c r="R61" t="n">
+        <v>7333959</v>
+      </c>
+      <c r="S61" t="n">
+        <v>7</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>16:34</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>16:34</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>135504216</v>
+      </c>
+      <c r="B62" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Tellejåkk, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>719949</v>
+      </c>
+      <c r="R62" t="n">
+        <v>7334163</v>
+      </c>
+      <c r="S62" t="n">
+        <v>9</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>135504195</v>
+      </c>
+      <c r="B63" t="n">
+        <v>79963</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Tellejokk, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>720165</v>
+      </c>
+      <c r="R63" t="n">
+        <v>7334136</v>
+      </c>
+      <c r="S63" t="n">
+        <v>5</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>15:57</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>15:57</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>135504215</v>
+      </c>
+      <c r="B64" t="n">
+        <v>79963</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Tellejåkk, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>719957</v>
+      </c>
+      <c r="R64" t="n">
+        <v>7334133</v>
+      </c>
+      <c r="S64" t="n">
+        <v>8</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>135504218</v>
+      </c>
+      <c r="B65" t="n">
+        <v>79963</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Tellejåkk, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>719946</v>
+      </c>
+      <c r="R65" t="n">
+        <v>7334187</v>
+      </c>
+      <c r="S65" t="n">
+        <v>8</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>129000484</v>
+      </c>
+      <c r="B66" t="n">
+        <v>93228</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>232140</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Tajgataggsvamp</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Phellodon secretus</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Niemelä &amp; Kinnunen</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Tellejåkk, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>719825</v>
+      </c>
+      <c r="R66" t="n">
+        <v>7334177</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>129000485</v>
+      </c>
+      <c r="B67" t="n">
+        <v>93228</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>232140</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Tajgataggsvamp</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Phellodon secretus</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Niemelä &amp; Kinnunen</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Tellejåkk, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>720125</v>
+      </c>
+      <c r="R67" t="n">
+        <v>7334096</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>135504179</v>
+      </c>
+      <c r="B68" t="n">
+        <v>79396</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Tellejokk, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>719837</v>
+      </c>
+      <c r="R68" t="n">
+        <v>7334083</v>
+      </c>
+      <c r="S68" t="n">
+        <v>5</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>135504186</v>
+      </c>
+      <c r="B69" t="n">
+        <v>79396</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Tellejokk, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>719929</v>
+      </c>
+      <c r="R69" t="n">
+        <v>7334206</v>
+      </c>
+      <c r="S69" t="n">
+        <v>6</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>13:49</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>13:49</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>135504224</v>
+      </c>
+      <c r="B70" t="n">
+        <v>93292</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>6331648</v>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Phellodon aquiloniniger</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>A.M.Ainsw. &amp; Svantesson</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Tellejåkk, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>720052</v>
+      </c>
+      <c r="R70" t="n">
+        <v>7334191</v>
+      </c>
+      <c r="S70" t="n">
+        <v>6</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF70" t="inlineStr"/>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 25608-2026 artfynd.xlsx
+++ b/artfynd/A 25608-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY70"/>
+  <dimension ref="A1:AY71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6219,48 +6219,56 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>135504205</v>
+        <v>135524852</v>
       </c>
       <c r="B55" t="n">
-        <v>98066</v>
+        <v>58136</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>221941</v>
+        <v>103021</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Tellejåkk, Lu lm</t>
+          <t>Tellejokk, Lu lm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>719826</v>
+        <v>719958</v>
       </c>
       <c r="R55" t="n">
-        <v>7334115</v>
+        <v>7334111</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6287,19 +6295,9 @@
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>10:48</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>10:48</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6314,22 +6312,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>135504197</v>
+        <v>135504205</v>
       </c>
       <c r="B56" t="n">
-        <v>99217</v>
+        <v>98066</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6337,37 +6335,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>221952</v>
+        <v>221941</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Tellejokk, Lu lm</t>
+          <t>Tellejåkk, Lu lm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>720196</v>
+        <v>719826</v>
       </c>
       <c r="R56" t="n">
-        <v>7334052</v>
+        <v>7334115</v>
       </c>
       <c r="S56" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6396,7 +6394,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6406,7 +6404,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6421,60 +6419,60 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>80984484</v>
+        <v>135504197</v>
       </c>
       <c r="B57" t="n">
-        <v>79085</v>
+        <v>99217</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>228912</v>
+        <v>221952</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Pärlskalbäcken, Lu lm</t>
+          <t>Tellejokk, Lu lm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>720042</v>
+        <v>720196</v>
       </c>
       <c r="R57" t="n">
-        <v>7334030</v>
+        <v>7334052</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6498,12 +6496,22 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2019-08-11</t>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2019-08-11</t>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6518,22 +6526,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Sture Westerberg</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>135504183</v>
+        <v>80984484</v>
       </c>
       <c r="B58" t="n">
-        <v>79131</v>
+        <v>79085</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6561,17 +6569,17 @@
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Tellejokk, Lu lm</t>
+          <t>Pärlskalbäcken, Lu lm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>719960</v>
+        <v>720042</v>
       </c>
       <c r="R58" t="n">
-        <v>7334135</v>
+        <v>7334030</v>
       </c>
       <c r="S58" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6595,22 +6603,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>13:24</t>
+          <t>2019-08-11</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>13:24</t>
+          <t>2019-08-11</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6625,19 +6623,19 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Sture Westerberg</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Helena Björnström</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>135504189</v>
+        <v>135504183</v>
       </c>
       <c r="B59" t="n">
         <v>79131</v>
@@ -6672,10 +6670,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>719990</v>
+        <v>719960</v>
       </c>
       <c r="R59" t="n">
-        <v>7334219</v>
+        <v>7334135</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6707,7 +6705,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6717,7 +6715,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6744,7 +6742,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>135504193</v>
+        <v>135504189</v>
       </c>
       <c r="B60" t="n">
         <v>79131</v>
@@ -6779,13 +6777,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>720034</v>
+        <v>719990</v>
       </c>
       <c r="R60" t="n">
-        <v>7334183</v>
+        <v>7334219</v>
       </c>
       <c r="S60" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6814,7 +6812,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -6824,7 +6822,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6851,7 +6849,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>135504201</v>
+        <v>135504193</v>
       </c>
       <c r="B61" t="n">
         <v>79131</v>
@@ -6886,13 +6884,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>720188</v>
+        <v>720034</v>
       </c>
       <c r="R61" t="n">
-        <v>7333959</v>
+        <v>7334183</v>
       </c>
       <c r="S61" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6921,7 +6919,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -6931,7 +6929,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6958,7 +6956,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>135504216</v>
+        <v>135504201</v>
       </c>
       <c r="B62" t="n">
         <v>79131</v>
@@ -6989,17 +6987,17 @@
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Tellejåkk, Lu lm</t>
+          <t>Tellejokk, Lu lm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>719949</v>
+        <v>720188</v>
       </c>
       <c r="R62" t="n">
-        <v>7334163</v>
+        <v>7333959</v>
       </c>
       <c r="S62" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7028,7 +7026,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7038,7 +7036,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7053,22 +7051,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>135504195</v>
+        <v>135504216</v>
       </c>
       <c r="B63" t="n">
-        <v>79963</v>
+        <v>79131</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7076,37 +7074,37 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Tellejokk, Lu lm</t>
+          <t>Tellejåkk, Lu lm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>720165</v>
+        <v>719949</v>
       </c>
       <c r="R63" t="n">
-        <v>7334136</v>
+        <v>7334163</v>
       </c>
       <c r="S63" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7135,7 +7133,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7145,7 +7143,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7160,19 +7158,19 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>135504215</v>
+        <v>135504195</v>
       </c>
       <c r="B64" t="n">
         <v>79963</v>
@@ -7203,17 +7201,17 @@
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Tellejåkk, Lu lm</t>
+          <t>Tellejokk, Lu lm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>719957</v>
+        <v>720165</v>
       </c>
       <c r="R64" t="n">
-        <v>7334133</v>
+        <v>7334136</v>
       </c>
       <c r="S64" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7242,7 +7240,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7252,7 +7250,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7267,19 +7265,19 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>135504218</v>
+        <v>135504215</v>
       </c>
       <c r="B65" t="n">
         <v>79963</v>
@@ -7314,10 +7312,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>719946</v>
+        <v>719957</v>
       </c>
       <c r="R65" t="n">
-        <v>7334187</v>
+        <v>7334133</v>
       </c>
       <c r="S65" t="n">
         <v>8</v>
@@ -7349,7 +7347,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7359,7 +7357,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7386,52 +7384,48 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129000484</v>
+        <v>135504218</v>
       </c>
       <c r="B66" t="n">
-        <v>93228</v>
+        <v>79963</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>232140</v>
+        <v>229821</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Tellejåkk, Lu lm</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>719825</v>
+        <v>719946</v>
       </c>
       <c r="R66" t="n">
-        <v>7334177</v>
+        <v>7334187</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7455,17 +7449,22 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7480,19 +7479,19 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129000485</v>
+        <v>129000484</v>
       </c>
       <c r="B67" t="n">
         <v>93228</v>
@@ -7531,10 +7530,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>720125</v>
+        <v>719825</v>
       </c>
       <c r="R67" t="n">
-        <v>7334096</v>
+        <v>7334177</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7598,48 +7597,52 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>135504179</v>
+        <v>129000485</v>
       </c>
       <c r="B68" t="n">
-        <v>79396</v>
+        <v>93228</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>260591</v>
+        <v>232140</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>Niemelä &amp; Kinnunen</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Tellejokk, Lu lm</t>
+          <t>Tellejåkk, Lu lm</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>719837</v>
+        <v>720125</v>
       </c>
       <c r="R68" t="n">
-        <v>7334083</v>
+        <v>7334096</v>
       </c>
       <c r="S68" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7663,22 +7666,17 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>12:18</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>12:18</t>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7693,19 +7691,19 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>135504186</v>
+        <v>135504179</v>
       </c>
       <c r="B69" t="n">
         <v>79396</v>
@@ -7740,13 +7738,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>719929</v>
+        <v>719837</v>
       </c>
       <c r="R69" t="n">
-        <v>7334206</v>
+        <v>7334083</v>
       </c>
       <c r="S69" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7775,7 +7773,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7785,7 +7783,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7812,10 +7810,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>135504224</v>
+        <v>135504186</v>
       </c>
       <c r="B70" t="n">
-        <v>93292</v>
+        <v>79396</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7823,29 +7821,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6331648</v>
+        <v>260591</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Phellodon aquiloniniger</t>
+          <t>Bryoria fremontii</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>A.M.Ainsw. &amp; Svantesson</t>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Tellejåkk, Lu lm</t>
+          <t>Tellejokk, Lu lm</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>720052</v>
+        <v>719929</v>
       </c>
       <c r="R70" t="n">
-        <v>7334191</v>
+        <v>7334206</v>
       </c>
       <c r="S70" t="n">
         <v>6</v>
@@ -7877,7 +7880,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -7887,7 +7890,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7896,22 +7899,124 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>135504224</v>
+      </c>
+      <c r="B71" t="n">
+        <v>93292</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>6331648</v>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Phellodon aquiloniniger</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>A.M.Ainsw. &amp; Svantesson</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Tellejåkk, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>720052</v>
+      </c>
+      <c r="R71" t="n">
+        <v>7334191</v>
+      </c>
+      <c r="S71" t="n">
+        <v>6</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF71" t="inlineStr"/>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
           <t>Marie Persson</t>
         </is>
       </c>
-      <c r="AX70" t="inlineStr">
+      <c r="AX71" t="inlineStr">
         <is>
           <t>Marie Persson</t>
         </is>
       </c>
-      <c r="AY70" t="inlineStr"/>
+      <c r="AY71" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 25608-2026 artfynd.xlsx
+++ b/artfynd/A 25608-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY71"/>
+  <dimension ref="A1:AZ71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504188</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -881,6 +891,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16885666</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80984495</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1075,6 +1095,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80984496</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1182,6 +1207,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504199</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1289,6 +1319,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504204</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1386,6 +1421,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80984487</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1493,6 +1533,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504206</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1600,6 +1645,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504226</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1707,6 +1757,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504228</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1814,6 +1869,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504177</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1921,6 +1981,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504187</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2028,6 +2093,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504207</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2135,6 +2205,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504220</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2242,6 +2317,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504222</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2349,6 +2429,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504232</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2456,6 +2541,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504223</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2563,6 +2653,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504227</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2670,6 +2765,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504229</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2777,6 +2877,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504236</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2874,6 +2979,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80984497</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2971,6 +3081,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80984502</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3068,6 +3183,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80984503</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3165,6 +3285,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80984505</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3272,6 +3397,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504181</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3379,6 +3509,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504182</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3486,6 +3621,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504184</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3593,6 +3733,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504185</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3700,6 +3845,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504191</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3807,6 +3957,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504194</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3914,6 +4069,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504209</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4021,6 +4181,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504211</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4128,6 +4293,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504219</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4225,6 +4395,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80984479</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4322,6 +4497,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80984480</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4428,6 +4608,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129000486</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4534,6 +4719,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129000487</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4640,6 +4830,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129000489</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4742,6 +4937,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16885667</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4839,6 +5039,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80984477</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4955,6 +5160,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133925242</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5062,6 +5272,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504198</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5159,6 +5374,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80984490</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5256,6 +5476,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80984491</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5363,6 +5588,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504200</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5469,6 +5699,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129000491</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5576,6 +5811,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504214</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5683,6 +5923,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504235</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5780,6 +6025,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80984470</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5877,6 +6127,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80984481</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5984,6 +6239,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504190</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6104,6 +6364,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504192</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6216,6 +6481,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504212</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6321,6 +6591,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135524852</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6428,6 +6703,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504205</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6535,6 +6815,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504197</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6632,6 +6917,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80984484</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6739,6 +7029,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504183</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6846,6 +7141,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504189</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6953,6 +7253,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504193</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7060,6 +7365,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504201</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7167,6 +7477,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504216</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7274,6 +7589,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504195</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7381,6 +7701,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504215</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7488,6 +7813,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504218</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7594,6 +7924,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129000484</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7700,6 +8035,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129000485</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7807,6 +8147,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504179</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7914,6 +8259,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504186</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8017,8 +8367,85 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504224</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 25608-2026 artfynd.xlsx
+++ b/artfynd/A 25608-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135504188</v>
       </c>
       <c r="B2" t="n">
-        <v>83350</v>
+        <v>83390</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>135504199</v>
       </c>
       <c r="B6" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>135504204</v>
       </c>
       <c r="B7" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>135504206</v>
       </c>
       <c r="B9" t="n">
-        <v>92153</v>
+        <v>92195</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>135504226</v>
       </c>
       <c r="B10" t="n">
-        <v>92153</v>
+        <v>92195</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         <v>135504228</v>
       </c>
       <c r="B11" t="n">
-        <v>92153</v>
+        <v>92195</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
         <v>135504177</v>
       </c>
       <c r="B12" t="n">
-        <v>90997</v>
+        <v>91039</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1880,7 +1880,7 @@
         <v>135504187</v>
       </c>
       <c r="B13" t="n">
-        <v>90997</v>
+        <v>91039</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1992,7 +1992,7 @@
         <v>135504207</v>
       </c>
       <c r="B14" t="n">
-        <v>92027</v>
+        <v>92069</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2104,7 +2104,7 @@
         <v>135504220</v>
       </c>
       <c r="B15" t="n">
-        <v>92027</v>
+        <v>92069</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2216,7 +2216,7 @@
         <v>135504222</v>
       </c>
       <c r="B16" t="n">
-        <v>92027</v>
+        <v>92069</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2328,7 +2328,7 @@
         <v>135504232</v>
       </c>
       <c r="B17" t="n">
-        <v>92027</v>
+        <v>92069</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2440,7 +2440,7 @@
         <v>135504223</v>
       </c>
       <c r="B18" t="n">
-        <v>91896</v>
+        <v>91938</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2552,7 +2552,7 @@
         <v>135504227</v>
       </c>
       <c r="B19" t="n">
-        <v>91896</v>
+        <v>91938</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2664,7 +2664,7 @@
         <v>135504229</v>
       </c>
       <c r="B20" t="n">
-        <v>91896</v>
+        <v>91938</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2776,7 +2776,7 @@
         <v>135504236</v>
       </c>
       <c r="B21" t="n">
-        <v>93263</v>
+        <v>93305</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3296,7 +3296,7 @@
         <v>135504181</v>
       </c>
       <c r="B26" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3408,7 +3408,7 @@
         <v>135504182</v>
       </c>
       <c r="B27" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3520,7 +3520,7 @@
         <v>135504184</v>
       </c>
       <c r="B28" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3632,7 +3632,7 @@
         <v>135504185</v>
       </c>
       <c r="B29" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3744,7 +3744,7 @@
         <v>135504191</v>
       </c>
       <c r="B30" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3856,7 +3856,7 @@
         <v>135504194</v>
       </c>
       <c r="B31" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>135504209</v>
       </c>
       <c r="B32" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4080,7 +4080,7 @@
         <v>135504211</v>
       </c>
       <c r="B33" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4192,7 +4192,7 @@
         <v>135504219</v>
       </c>
       <c r="B34" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5171,7 +5171,7 @@
         <v>135504198</v>
       </c>
       <c r="B43" t="n">
-        <v>93255</v>
+        <v>93297</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5487,7 +5487,7 @@
         <v>135504200</v>
       </c>
       <c r="B46" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5710,7 +5710,7 @@
         <v>135504214</v>
       </c>
       <c r="B48" t="n">
-        <v>79130</v>
+        <v>79168</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5822,7 +5822,7 @@
         <v>135504235</v>
       </c>
       <c r="B49" t="n">
-        <v>79130</v>
+        <v>79168</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6138,7 +6138,7 @@
         <v>135504190</v>
       </c>
       <c r="B52" t="n">
-        <v>78377</v>
+        <v>78415</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6250,7 +6250,7 @@
         <v>135504192</v>
       </c>
       <c r="B53" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6375,7 +6375,7 @@
         <v>135504212</v>
       </c>
       <c r="B54" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6492,7 +6492,7 @@
         <v>135524852</v>
       </c>
       <c r="B55" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6602,7 +6602,7 @@
         <v>135504205</v>
       </c>
       <c r="B56" t="n">
-        <v>98066</v>
+        <v>98110</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6714,7 +6714,7 @@
         <v>135504197</v>
       </c>
       <c r="B57" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6928,7 +6928,7 @@
         <v>135504183</v>
       </c>
       <c r="B59" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7040,7 +7040,7 @@
         <v>135504189</v>
       </c>
       <c r="B60" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7152,7 +7152,7 @@
         <v>135504193</v>
       </c>
       <c r="B61" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7264,7 +7264,7 @@
         <v>135504201</v>
       </c>
       <c r="B62" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7376,7 +7376,7 @@
         <v>135504216</v>
       </c>
       <c r="B63" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7488,7 +7488,7 @@
         <v>135504195</v>
       </c>
       <c r="B64" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7600,7 +7600,7 @@
         <v>135504215</v>
       </c>
       <c r="B65" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7712,7 +7712,7 @@
         <v>135504218</v>
       </c>
       <c r="B66" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8046,7 +8046,7 @@
         <v>135504179</v>
       </c>
       <c r="B69" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8158,7 +8158,7 @@
         <v>135504186</v>
       </c>
       <c r="B70" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8270,7 +8270,7 @@
         <v>135504224</v>
       </c>
       <c r="B71" t="n">
-        <v>93292</v>
+        <v>93334</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8291,6 +8291,9 @@
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Tellejåkk, Lu lm</t>

--- a/artfynd/A 25608-2026 artfynd.xlsx
+++ b/artfynd/A 25608-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135504188</v>
       </c>
       <c r="B2" t="n">
-        <v>83390</v>
+        <v>83417</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>135504199</v>
       </c>
       <c r="B6" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>135504204</v>
       </c>
       <c r="B7" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>135504206</v>
       </c>
       <c r="B9" t="n">
-        <v>92195</v>
+        <v>92222</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>135504226</v>
       </c>
       <c r="B10" t="n">
-        <v>92195</v>
+        <v>92222</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         <v>135504228</v>
       </c>
       <c r="B11" t="n">
-        <v>92195</v>
+        <v>92222</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
         <v>135504177</v>
       </c>
       <c r="B12" t="n">
-        <v>91039</v>
+        <v>91066</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1880,7 +1880,7 @@
         <v>135504187</v>
       </c>
       <c r="B13" t="n">
-        <v>91039</v>
+        <v>91066</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1992,7 +1992,7 @@
         <v>135504207</v>
       </c>
       <c r="B14" t="n">
-        <v>92069</v>
+        <v>92096</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2104,7 +2104,7 @@
         <v>135504220</v>
       </c>
       <c r="B15" t="n">
-        <v>92069</v>
+        <v>92096</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2216,7 +2216,7 @@
         <v>135504222</v>
       </c>
       <c r="B16" t="n">
-        <v>92069</v>
+        <v>92096</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2328,7 +2328,7 @@
         <v>135504232</v>
       </c>
       <c r="B17" t="n">
-        <v>92069</v>
+        <v>92096</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2440,7 +2440,7 @@
         <v>135504223</v>
       </c>
       <c r="B18" t="n">
-        <v>91938</v>
+        <v>91965</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2552,7 +2552,7 @@
         <v>135504227</v>
       </c>
       <c r="B19" t="n">
-        <v>91938</v>
+        <v>91965</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2664,7 +2664,7 @@
         <v>135504229</v>
       </c>
       <c r="B20" t="n">
-        <v>91938</v>
+        <v>91965</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2776,7 +2776,7 @@
         <v>135504236</v>
       </c>
       <c r="B21" t="n">
-        <v>93305</v>
+        <v>93332</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3296,7 +3296,7 @@
         <v>135504181</v>
       </c>
       <c r="B26" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3408,7 +3408,7 @@
         <v>135504182</v>
       </c>
       <c r="B27" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3520,7 +3520,7 @@
         <v>135504184</v>
       </c>
       <c r="B28" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3632,7 +3632,7 @@
         <v>135504185</v>
       </c>
       <c r="B29" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3744,7 +3744,7 @@
         <v>135504191</v>
       </c>
       <c r="B30" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3856,7 +3856,7 @@
         <v>135504194</v>
       </c>
       <c r="B31" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>135504209</v>
       </c>
       <c r="B32" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4080,7 +4080,7 @@
         <v>135504211</v>
       </c>
       <c r="B33" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4192,7 +4192,7 @@
         <v>135504219</v>
       </c>
       <c r="B34" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5171,7 +5171,7 @@
         <v>135504198</v>
       </c>
       <c r="B43" t="n">
-        <v>93297</v>
+        <v>93324</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5487,7 +5487,7 @@
         <v>135504200</v>
       </c>
       <c r="B46" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5710,7 +5710,7 @@
         <v>135504214</v>
       </c>
       <c r="B48" t="n">
-        <v>79168</v>
+        <v>79195</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5822,7 +5822,7 @@
         <v>135504235</v>
       </c>
       <c r="B49" t="n">
-        <v>79168</v>
+        <v>79195</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6138,7 +6138,7 @@
         <v>135504190</v>
       </c>
       <c r="B52" t="n">
-        <v>78415</v>
+        <v>78442</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6602,7 +6602,7 @@
         <v>135504205</v>
       </c>
       <c r="B56" t="n">
-        <v>98110</v>
+        <v>98137</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6714,7 +6714,7 @@
         <v>135504197</v>
       </c>
       <c r="B57" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6928,7 +6928,7 @@
         <v>135504183</v>
       </c>
       <c r="B59" t="n">
-        <v>79169</v>
+        <v>79196</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7040,7 +7040,7 @@
         <v>135504189</v>
       </c>
       <c r="B60" t="n">
-        <v>79169</v>
+        <v>79196</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7152,7 +7152,7 @@
         <v>135504193</v>
       </c>
       <c r="B61" t="n">
-        <v>79169</v>
+        <v>79196</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7264,7 +7264,7 @@
         <v>135504201</v>
       </c>
       <c r="B62" t="n">
-        <v>79169</v>
+        <v>79196</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7376,7 +7376,7 @@
         <v>135504216</v>
       </c>
       <c r="B63" t="n">
-        <v>79169</v>
+        <v>79196</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7488,7 +7488,7 @@
         <v>135504195</v>
       </c>
       <c r="B64" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7600,7 +7600,7 @@
         <v>135504215</v>
       </c>
       <c r="B65" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7712,7 +7712,7 @@
         <v>135504218</v>
       </c>
       <c r="B66" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8046,7 +8046,7 @@
         <v>135504179</v>
       </c>
       <c r="B69" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8158,7 +8158,7 @@
         <v>135504186</v>
       </c>
       <c r="B70" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8270,7 +8270,7 @@
         <v>135504224</v>
       </c>
       <c r="B71" t="n">
-        <v>93334</v>
+        <v>93361</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>

--- a/artfynd/A 25608-2026 artfynd.xlsx
+++ b/artfynd/A 25608-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ25"/>
+  <dimension ref="A1:AZ71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>16885666</v>
+        <v>135504188</v>
       </c>
       <c r="B2" t="n">
-        <v>78993</v>
+        <v>83420</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>353</v>
+        <v>308</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>1200 m S Tellejåkk, Lu lm</t>
+          <t>Tellejokk, Lu lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>720077</v>
+        <v>719995</v>
       </c>
       <c r="R2" t="n">
-        <v>7333978</v>
+        <v>7334207</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,17 +745,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2014-08-18</t>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2014-08-18</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Sveaskog naturvärdesinventering, inventerare: Rasmus Häggqvist</t>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,24 +775,24 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Caspar Ström</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Sveaskog genom Johan Ekenstedt</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/16885666</t>
+          <t>https://artportalen.se/Sighting/135504188</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>80984495</v>
+        <v>16885666</v>
       </c>
       <c r="B3" t="n">
         <v>78993</v>
@@ -818,14 +823,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Pärlskalbäcken, Lu lm</t>
+          <t>1200 m S Tellejåkk, Lu lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>720110</v>
+        <v>720077</v>
       </c>
       <c r="R3" t="n">
-        <v>7334046</v>
+        <v>7333978</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,12 +857,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2019-08-11</t>
+          <t>2014-08-18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2019-08-11</t>
+          <t>2014-08-18</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Sveaskog naturvärdesinventering, inventerare: Rasmus Häggqvist</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -872,24 +882,24 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Sture Westerberg</t>
+          <t>Caspar Ström</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Sveaskog genom Johan Ekenstedt</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80984495</t>
+          <t>https://artportalen.se/Sighting/16885666</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>80984496</v>
+        <v>80984495</v>
       </c>
       <c r="B4" t="n">
         <v>78993</v>
@@ -924,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>719834</v>
+        <v>720110</v>
       </c>
       <c r="R4" t="n">
-        <v>7334183</v>
+        <v>7334046</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -985,38 +995,38 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80984496</t>
+          <t>https://artportalen.se/Sighting/80984495</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>80984487</v>
+        <v>80984496</v>
       </c>
       <c r="B5" t="n">
-        <v>92083</v>
+        <v>78993</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1503</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>719823</v>
+        <v>719834</v>
       </c>
       <c r="R5" t="n">
-        <v>7334170</v>
+        <v>7334183</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1087,16 +1097,16 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80984487</t>
+          <t>https://artportalen.se/Sighting/80984496</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>80984497</v>
+        <v>135504199</v>
       </c>
       <c r="B6" t="n">
-        <v>93197</v>
+        <v>79107</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1104,37 +1114,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Pärlskalbäcken, Lu lm</t>
+          <t>Tellejokk, Lu lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>719812</v>
+        <v>720174</v>
       </c>
       <c r="R6" t="n">
-        <v>7334171</v>
+        <v>7333975</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1158,12 +1168,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2019-08-11</t>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2019-08-11</t>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1178,27 +1198,27 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Sture Westerberg</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80984497</t>
+          <t>https://artportalen.se/Sighting/135504199</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>80984502</v>
+        <v>135504204</v>
       </c>
       <c r="B7" t="n">
-        <v>93197</v>
+        <v>79107</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1206,37 +1226,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Pärlskalbäcken, Lu lm</t>
+          <t>Tellejåkk, Lu lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>720322</v>
+        <v>719841</v>
       </c>
       <c r="R7" t="n">
-        <v>7334224</v>
+        <v>7334205</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1260,12 +1280,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2019-08-11</t>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2019-08-11</t>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1280,49 +1310,49 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Sture Westerberg</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80984502</t>
+          <t>https://artportalen.se/Sighting/135504204</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>80984503</v>
+        <v>80984487</v>
       </c>
       <c r="B8" t="n">
-        <v>93197</v>
+        <v>92083</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>1503</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1332,10 +1362,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>720316</v>
+        <v>719823</v>
       </c>
       <c r="R8" t="n">
-        <v>7334161</v>
+        <v>7334170</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1393,54 +1423,54 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80984503</t>
+          <t>https://artportalen.se/Sighting/80984487</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>80984505</v>
+        <v>135504206</v>
       </c>
       <c r="B9" t="n">
-        <v>93197</v>
+        <v>92227</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>1503</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Pärlskalbäcken, Lu lm</t>
+          <t>Tellejåkk, Lu lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>720321</v>
+        <v>719795</v>
       </c>
       <c r="R9" t="n">
-        <v>7334098</v>
+        <v>7334134</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1464,12 +1494,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2019-08-11</t>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2019-08-11</t>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1484,27 +1524,27 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Sture Westerberg</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80984505</t>
+          <t>https://artportalen.se/Sighting/135504206</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>80984479</v>
+        <v>135504226</v>
       </c>
       <c r="B10" t="n">
-        <v>93201</v>
+        <v>92227</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1512,37 +1552,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4365</v>
+        <v>1503</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Pärlskalbäcken, Lu lm</t>
+          <t>Tellejåkk, Lu lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>720116</v>
+        <v>720053</v>
       </c>
       <c r="R10" t="n">
-        <v>7334051</v>
+        <v>7334194</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1566,12 +1606,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2019-08-11</t>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2019-08-11</t>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1586,27 +1636,27 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Sture Westerberg</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80984479</t>
+          <t>https://artportalen.se/Sighting/135504226</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>80984480</v>
+        <v>135504228</v>
       </c>
       <c r="B11" t="n">
-        <v>93201</v>
+        <v>92227</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1614,37 +1664,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4365</v>
+        <v>1503</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Pärlskalbäcken, Lu lm</t>
+          <t>Tellejåkk, Lu lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>720093</v>
+        <v>720162</v>
       </c>
       <c r="R11" t="n">
-        <v>7334024</v>
+        <v>7334159</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1668,12 +1718,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2019-08-11</t>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2019-08-11</t>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1688,27 +1748,27 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Sture Westerberg</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80984480</t>
+          <t>https://artportalen.se/Sighting/135504228</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129000486</v>
+        <v>135504177</v>
       </c>
       <c r="B12" t="n">
-        <v>93209</v>
+        <v>91069</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1716,41 +1776,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4366</v>
+        <v>1962</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Tellejåkk, Lu lm</t>
+          <t>Tellejokk, Lu lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>720161</v>
+        <v>719793</v>
       </c>
       <c r="R12" t="n">
-        <v>7334167</v>
+        <v>7334135</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1774,17 +1830,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1799,27 +1860,27 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129000486</t>
+          <t>https://artportalen.se/Sighting/135504177</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129000487</v>
+        <v>135504187</v>
       </c>
       <c r="B13" t="n">
-        <v>93209</v>
+        <v>91069</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1827,41 +1888,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4366</v>
+        <v>1962</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Tellejåkk, Lu lm</t>
+          <t>Tellejokk, Lu lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>720349</v>
+        <v>719933</v>
       </c>
       <c r="R13" t="n">
-        <v>7334152</v>
+        <v>7334218</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1885,17 +1942,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1910,27 +1972,27 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129000487</t>
+          <t>https://artportalen.se/Sighting/135504187</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129000489</v>
+        <v>135504207</v>
       </c>
       <c r="B14" t="n">
-        <v>93209</v>
+        <v>92101</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1938,41 +2000,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4366</v>
+        <v>2079</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(S.Lundell) Parmasto</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Tellejåkk, Lu lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>720534</v>
+        <v>719794</v>
       </c>
       <c r="R14" t="n">
-        <v>7334112</v>
+        <v>7334139</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1996,17 +2054,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2021,27 +2084,27 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129000489</t>
+          <t>https://artportalen.se/Sighting/135504207</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>16885667</v>
+        <v>135504220</v>
       </c>
       <c r="B15" t="n">
-        <v>91930</v>
+        <v>92101</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2049,37 +2112,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5442</v>
+        <v>2079</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>1100 m S Tellejåkk, Lu lm</t>
+          <t>Tellejåkk, Lu lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>720126</v>
+        <v>719978</v>
       </c>
       <c r="R15" t="n">
-        <v>7334106</v>
+        <v>7334223</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2103,17 +2166,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2014-08-18</t>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2014-08-18</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Sveaskog naturvärdesinventering, inventerare: Rasmus Häggqvist</t>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2128,27 +2196,27 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Caspar Ström</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Sveaskog genom Johan Ekenstedt</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/16885667</t>
+          <t>https://artportalen.se/Sighting/135504220</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>80984477</v>
+        <v>135504222</v>
       </c>
       <c r="B16" t="n">
-        <v>91930</v>
+        <v>92101</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2156,37 +2224,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5442</v>
+        <v>2079</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Pärlskalbäcken, Lu lm</t>
+          <t>Tellejåkk, Lu lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>720041</v>
+        <v>719990</v>
       </c>
       <c r="R16" t="n">
-        <v>7334058</v>
+        <v>7334243</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2210,12 +2278,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2019-08-11</t>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2019-08-11</t>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2230,27 +2308,27 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Sture Westerberg</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80984477</t>
+          <t>https://artportalen.se/Sighting/135504222</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133925242</v>
+        <v>135504232</v>
       </c>
       <c r="B17" t="n">
-        <v>91995</v>
+        <v>92101</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2258,41 +2336,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5442</v>
+        <v>2079</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(S.Lundell) Parmasto</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Tellejåkk, Lu lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>720043</v>
+        <v>720167</v>
       </c>
       <c r="R17" t="n">
-        <v>7333956</v>
+        <v>7334013</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2316,27 +2390,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:46</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2351,65 +2420,65 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133925242</t>
+          <t>https://artportalen.se/Sighting/135504232</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>80984490</v>
+        <v>135504223</v>
       </c>
       <c r="B18" t="n">
-        <v>79327</v>
+        <v>91970</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>3242</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Pärlskalbäcken, Lu lm</t>
+          <t>Tellejåkk, Lu lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>719772</v>
+        <v>720026</v>
       </c>
       <c r="R18" t="n">
-        <v>7334154</v>
+        <v>7334208</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2433,12 +2502,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2019-08-11</t>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2019-08-11</t>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2453,65 +2532,65 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Sture Westerberg</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80984490</t>
+          <t>https://artportalen.se/Sighting/135504223</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>80984491</v>
+        <v>135504227</v>
       </c>
       <c r="B19" t="n">
-        <v>79327</v>
+        <v>91970</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>3242</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Pärlskalbäcken, Lu lm</t>
+          <t>Tellejåkk, Lu lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>720366</v>
+        <v>720066</v>
       </c>
       <c r="R19" t="n">
-        <v>7334007</v>
+        <v>7334187</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2535,12 +2614,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2019-08-11</t>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2019-08-11</t>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2555,27 +2644,27 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Sture Westerberg</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80984491</t>
+          <t>https://artportalen.se/Sighting/135504227</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129000491</v>
+        <v>135504229</v>
       </c>
       <c r="B20" t="n">
-        <v>79084</v>
+        <v>91970</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2583,41 +2672,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>3242</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Tellejåkk, Lu lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>720506</v>
+        <v>720160</v>
       </c>
       <c r="R20" t="n">
-        <v>7334145</v>
+        <v>7334058</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2641,17 +2726,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2666,27 +2756,27 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129000491</t>
+          <t>https://artportalen.se/Sighting/135504229</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>80984470</v>
+        <v>135504236</v>
       </c>
       <c r="B21" t="n">
-        <v>79946</v>
+        <v>93337</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2694,37 +2784,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>4361</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Pärlskalbäcken, Lu lm</t>
+          <t>Tellejåkk, Lu lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>719860</v>
+        <v>720151</v>
       </c>
       <c r="R21" t="n">
-        <v>7334190</v>
+        <v>7334030</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2748,12 +2838,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2019-08-11</t>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2019-08-11</t>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2768,49 +2868,49 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Sture Westerberg</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80984470</t>
+          <t>https://artportalen.se/Sighting/135504236</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>80984481</v>
+        <v>80984497</v>
       </c>
       <c r="B22" t="n">
-        <v>80336</v>
+        <v>93197</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6456</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2820,10 +2920,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>720052</v>
+        <v>719812</v>
       </c>
       <c r="R22" t="n">
-        <v>7334094</v>
+        <v>7334171</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2881,16 +2981,16 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80984481</t>
+          <t>https://artportalen.se/Sighting/80984497</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>80984484</v>
+        <v>80984502</v>
       </c>
       <c r="B23" t="n">
-        <v>79085</v>
+        <v>93197</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2898,21 +2998,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2922,10 +3022,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>720042</v>
+        <v>720322</v>
       </c>
       <c r="R23" t="n">
-        <v>7334030</v>
+        <v>7334224</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2983,55 +3083,51 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80984484</t>
+          <t>https://artportalen.se/Sighting/80984502</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129000484</v>
+        <v>80984503</v>
       </c>
       <c r="B24" t="n">
-        <v>93228</v>
+        <v>93197</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>232140</v>
+        <v>4364</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Tellejåkk, Lu lm</t>
+          <t>Pärlskalbäcken, Lu lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>719825</v>
+        <v>720316</v>
       </c>
       <c r="R24" t="n">
-        <v>7334177</v>
+        <v>7334161</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3058,17 +3154,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2019-08-11</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2019-08-11</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3083,66 +3174,62 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Sture Westerberg</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Helena Björnström</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129000484</t>
+          <t>https://artportalen.se/Sighting/80984503</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129000485</v>
+        <v>80984505</v>
       </c>
       <c r="B25" t="n">
-        <v>93228</v>
+        <v>93197</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>232140</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Tellejåkk, Lu lm</t>
+          <t>Pärlskalbäcken, Lu lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>720125</v>
+        <v>720321</v>
       </c>
       <c r="R25" t="n">
-        <v>7334096</v>
+        <v>7334098</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3169,17 +3256,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2019-08-11</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2019-08-11</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3194,18 +3276,5103 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Sture Westerberg</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Helena Björnström</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/80984505</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>135504181</v>
+      </c>
+      <c r="B26" t="n">
+        <v>93345</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Tellejokk, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>719937</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7334093</v>
+      </c>
+      <c r="S26" t="n">
+        <v>6</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>12:36</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>12:36</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504181</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>135504182</v>
+      </c>
+      <c r="B27" t="n">
+        <v>93345</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Tellejokk, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>719942</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7334096</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504182</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>135504184</v>
+      </c>
+      <c r="B28" t="n">
+        <v>93345</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Tellejokk, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>719948</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7334156</v>
+      </c>
+      <c r="S28" t="n">
+        <v>6</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504184</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>135504185</v>
+      </c>
+      <c r="B29" t="n">
+        <v>93345</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Tellejokk, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>719927</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7334199</v>
+      </c>
+      <c r="S29" t="n">
+        <v>6</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>13:47</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>13:47</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504185</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>135504191</v>
+      </c>
+      <c r="B30" t="n">
+        <v>93345</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Tellejokk, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>719999</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7334211</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>15:32</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>15:32</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504191</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>135504194</v>
+      </c>
+      <c r="B31" t="n">
+        <v>93345</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Tellejokk, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>720094</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7334186</v>
+      </c>
+      <c r="S31" t="n">
+        <v>6</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504194</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>135504209</v>
+      </c>
+      <c r="B32" t="n">
+        <v>93345</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Tellejåkk, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>719848</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7334077</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>12:16</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>12:16</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504209</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>135504211</v>
+      </c>
+      <c r="B33" t="n">
+        <v>93345</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Tellejåkk, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>719865</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7334082</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>12:27</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>12:27</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504211</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>135504219</v>
+      </c>
+      <c r="B34" t="n">
+        <v>93345</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Tellejåkk, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>719953</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7334191</v>
+      </c>
+      <c r="S34" t="n">
+        <v>9</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>13:48</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>13:48</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504219</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>80984479</v>
+      </c>
+      <c r="B35" t="n">
+        <v>93201</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>4365</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Smalfotad taggsvamp</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Hydnellum gracilipes</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Pärlskalbäcken, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>720116</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7334051</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2019-08-11</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2019-08-11</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Sture Westerberg</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80984479</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>80984480</v>
+      </c>
+      <c r="B36" t="n">
+        <v>93201</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>4365</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Smalfotad taggsvamp</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Hydnellum gracilipes</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Pärlskalbäcken, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>720093</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7334024</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2019-08-11</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2019-08-11</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Sture Westerberg</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80984480</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>129000486</v>
+      </c>
+      <c r="B37" t="n">
+        <v>93209</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Tellejåkk, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>720161</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7334167</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129000486</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>129000487</v>
+      </c>
+      <c r="B38" t="n">
+        <v>93209</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Tellejåkk, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>720349</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7334152</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129000487</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>129000489</v>
+      </c>
+      <c r="B39" t="n">
+        <v>93209</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Tellejåkk, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>720534</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7334112</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129000489</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>16885667</v>
+      </c>
+      <c r="B40" t="n">
+        <v>91930</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>1100 m S Tellejåkk, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>720126</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7334106</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2014-08-18</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2014-08-18</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Sveaskog naturvärdesinventering, inventerare: Rasmus Häggqvist</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Sveaskog genom Johan Ekenstedt</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16885667</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>80984477</v>
+      </c>
+      <c r="B41" t="n">
+        <v>91930</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Pärlskalbäcken, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>720041</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7334058</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2019-08-11</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2019-08-11</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Sture Westerberg</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80984477</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>133925242</v>
+      </c>
+      <c r="B42" t="n">
+        <v>91995</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Tellejåkk, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>720043</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7333956</v>
+      </c>
+      <c r="S42" t="n">
+        <v>25</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>09:46</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>09:46</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133925242</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>135504198</v>
+      </c>
+      <c r="B43" t="n">
+        <v>93329</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>6055</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Spadskinn</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Stereopsis vitellina</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(S.Lundell) D.A.Reid</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Tellejokk, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>720172</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7333985</v>
+      </c>
+      <c r="S43" t="n">
+        <v>6</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>16:23</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>16:23</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504198</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>80984490</v>
+      </c>
+      <c r="B44" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Pärlskalbäcken, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>719772</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7334154</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2019-08-11</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2019-08-11</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Sture Westerberg</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80984490</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>80984491</v>
+      </c>
+      <c r="B45" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Pärlskalbäcken, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>720366</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7334007</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2019-08-11</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2019-08-11</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Sture Westerberg</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80984491</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>135504200</v>
+      </c>
+      <c r="B46" t="n">
+        <v>78844</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Tellejokk, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>720190</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7333962</v>
+      </c>
+      <c r="S46" t="n">
+        <v>5</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>16:33</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>16:33</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504200</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>129000491</v>
+      </c>
+      <c r="B47" t="n">
+        <v>79084</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Tellejåkk, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>720506</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7334145</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129000491</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>135504214</v>
+      </c>
+      <c r="B48" t="n">
+        <v>79198</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Tellejåkk, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>719950</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7334140</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504214</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>135504235</v>
+      </c>
+      <c r="B49" t="n">
+        <v>79198</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Tellejåkk, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>720195</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7333954</v>
+      </c>
+      <c r="S49" t="n">
+        <v>5</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>16:34</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>16:34</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504235</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>80984470</v>
+      </c>
+      <c r="B50" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Pärlskalbäcken, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>719860</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7334190</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2019-08-11</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2019-08-11</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Sture Westerberg</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80984470</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>80984481</v>
+      </c>
+      <c r="B51" t="n">
+        <v>80336</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Pärlskalbäcken, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>720052</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7334094</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2019-08-11</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2019-08-11</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Sture Westerberg</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80984481</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>135504190</v>
+      </c>
+      <c r="B52" t="n">
+        <v>78445</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>6487</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Blågrå svartspik</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis fennica</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Tellejokk, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>720004</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7334229</v>
+      </c>
+      <c r="S52" t="n">
+        <v>5</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504190</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>135504192</v>
+      </c>
+      <c r="B53" t="n">
+        <v>57167</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Tellejokk, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>720018</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7334206</v>
+      </c>
+      <c r="S53" t="n">
+        <v>5</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Spillning</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504192</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>135504212</v>
+      </c>
+      <c r="B54" t="n">
+        <v>57167</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Tellejåkk, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>719954</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7334093</v>
+      </c>
+      <c r="S54" t="n">
+        <v>8</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Spillning</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504212</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>135524852</v>
+      </c>
+      <c r="B55" t="n">
+        <v>58141</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Tellejokk, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>719958</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7334111</v>
+      </c>
+      <c r="S55" t="n">
+        <v>9</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135524852</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>135504205</v>
+      </c>
+      <c r="B56" t="n">
+        <v>98142</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Tellejåkk, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>719826</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7334115</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504205</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>135504197</v>
+      </c>
+      <c r="B57" t="n">
+        <v>99296</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Tellejokk, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>720196</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7334052</v>
+      </c>
+      <c r="S57" t="n">
+        <v>5</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>16:09</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>16:09</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504197</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>80984484</v>
+      </c>
+      <c r="B58" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Pärlskalbäcken, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>720042</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7334030</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2019-08-11</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2019-08-11</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Sture Westerberg</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80984484</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>135504183</v>
+      </c>
+      <c r="B59" t="n">
+        <v>79199</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Tellejokk, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>719960</v>
+      </c>
+      <c r="R59" t="n">
+        <v>7334135</v>
+      </c>
+      <c r="S59" t="n">
+        <v>5</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504183</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>135504189</v>
+      </c>
+      <c r="B60" t="n">
+        <v>79199</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Tellejokk, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>719990</v>
+      </c>
+      <c r="R60" t="n">
+        <v>7334219</v>
+      </c>
+      <c r="S60" t="n">
+        <v>5</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504189</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>135504193</v>
+      </c>
+      <c r="B61" t="n">
+        <v>79199</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Tellejokk, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>720034</v>
+      </c>
+      <c r="R61" t="n">
+        <v>7334183</v>
+      </c>
+      <c r="S61" t="n">
+        <v>6</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>15:41</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>15:41</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504193</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>135504201</v>
+      </c>
+      <c r="B62" t="n">
+        <v>79199</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Tellejokk, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>720188</v>
+      </c>
+      <c r="R62" t="n">
+        <v>7333959</v>
+      </c>
+      <c r="S62" t="n">
+        <v>7</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>16:34</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>16:34</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504201</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>135504216</v>
+      </c>
+      <c r="B63" t="n">
+        <v>79199</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Tellejåkk, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>719949</v>
+      </c>
+      <c r="R63" t="n">
+        <v>7334163</v>
+      </c>
+      <c r="S63" t="n">
+        <v>9</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504216</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>135504195</v>
+      </c>
+      <c r="B64" t="n">
+        <v>80031</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Tellejokk, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>720165</v>
+      </c>
+      <c r="R64" t="n">
+        <v>7334136</v>
+      </c>
+      <c r="S64" t="n">
+        <v>5</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>15:57</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>15:57</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504195</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>135504215</v>
+      </c>
+      <c r="B65" t="n">
+        <v>80031</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Tellejåkk, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>719957</v>
+      </c>
+      <c r="R65" t="n">
+        <v>7334133</v>
+      </c>
+      <c r="S65" t="n">
+        <v>8</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504215</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>135504218</v>
+      </c>
+      <c r="B66" t="n">
+        <v>80031</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Tellejåkk, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>719946</v>
+      </c>
+      <c r="R66" t="n">
+        <v>7334187</v>
+      </c>
+      <c r="S66" t="n">
+        <v>8</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504218</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>129000484</v>
+      </c>
+      <c r="B67" t="n">
+        <v>93228</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>232140</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Tajgataggsvamp</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Phellodon secretus</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Niemelä &amp; Kinnunen</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Tellejåkk, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>719825</v>
+      </c>
+      <c r="R67" t="n">
+        <v>7334177</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129000484</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>129000485</v>
+      </c>
+      <c r="B68" t="n">
+        <v>93228</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>232140</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Tajgataggsvamp</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Phellodon secretus</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Niemelä &amp; Kinnunen</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Tellejåkk, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>720125</v>
+      </c>
+      <c r="R68" t="n">
+        <v>7334096</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/129000485</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>135504179</v>
+      </c>
+      <c r="B69" t="n">
+        <v>79464</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Tellejokk, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>719837</v>
+      </c>
+      <c r="R69" t="n">
+        <v>7334083</v>
+      </c>
+      <c r="S69" t="n">
+        <v>5</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504179</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>135504186</v>
+      </c>
+      <c r="B70" t="n">
+        <v>79464</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Tellejokk, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>719929</v>
+      </c>
+      <c r="R70" t="n">
+        <v>7334206</v>
+      </c>
+      <c r="S70" t="n">
+        <v>6</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>13:49</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>13:49</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504186</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>135504224</v>
+      </c>
+      <c r="B71" t="n">
+        <v>93366</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>6331648</v>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Phellodon aquiloniniger</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>A.M.Ainsw. &amp; Svantesson</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Tellejåkk, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>720052</v>
+      </c>
+      <c r="R71" t="n">
+        <v>7334191</v>
+      </c>
+      <c r="S71" t="n">
+        <v>6</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF71" t="inlineStr"/>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504224</t>
         </is>
       </c>
     </row>
@@ -3235,6 +8402,52 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 25608-2026 artfynd.xlsx
+++ b/artfynd/A 25608-2026 artfynd.xlsx
@@ -1432,7 +1432,7 @@
         <v>135504206</v>
       </c>
       <c r="B9" t="n">
-        <v>92227</v>
+        <v>92229</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>135504226</v>
       </c>
       <c r="B10" t="n">
-        <v>92227</v>
+        <v>92229</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         <v>135504228</v>
       </c>
       <c r="B11" t="n">
-        <v>92227</v>
+        <v>92229</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
         <v>135504177</v>
       </c>
       <c r="B12" t="n">
-        <v>91069</v>
+        <v>91071</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1880,7 +1880,7 @@
         <v>135504187</v>
       </c>
       <c r="B13" t="n">
-        <v>91069</v>
+        <v>91071</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1992,7 +1992,7 @@
         <v>135504207</v>
       </c>
       <c r="B14" t="n">
-        <v>92101</v>
+        <v>92103</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2104,7 +2104,7 @@
         <v>135504220</v>
       </c>
       <c r="B15" t="n">
-        <v>92101</v>
+        <v>92103</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2216,7 +2216,7 @@
         <v>135504222</v>
       </c>
       <c r="B16" t="n">
-        <v>92101</v>
+        <v>92103</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2328,7 +2328,7 @@
         <v>135504232</v>
       </c>
       <c r="B17" t="n">
-        <v>92101</v>
+        <v>92103</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2440,7 +2440,7 @@
         <v>135504223</v>
       </c>
       <c r="B18" t="n">
-        <v>91970</v>
+        <v>91972</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2552,7 +2552,7 @@
         <v>135504227</v>
       </c>
       <c r="B19" t="n">
-        <v>91970</v>
+        <v>91972</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2664,7 +2664,7 @@
         <v>135504229</v>
       </c>
       <c r="B20" t="n">
-        <v>91970</v>
+        <v>91972</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2776,7 +2776,7 @@
         <v>135504236</v>
       </c>
       <c r="B21" t="n">
-        <v>93337</v>
+        <v>93339</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3296,7 +3296,7 @@
         <v>135504181</v>
       </c>
       <c r="B26" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3408,7 +3408,7 @@
         <v>135504182</v>
       </c>
       <c r="B27" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3520,7 +3520,7 @@
         <v>135504184</v>
       </c>
       <c r="B28" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3632,7 +3632,7 @@
         <v>135504185</v>
       </c>
       <c r="B29" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3744,7 +3744,7 @@
         <v>135504191</v>
       </c>
       <c r="B30" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3856,7 +3856,7 @@
         <v>135504194</v>
       </c>
       <c r="B31" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>135504209</v>
       </c>
       <c r="B32" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4080,7 +4080,7 @@
         <v>135504211</v>
       </c>
       <c r="B33" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4192,7 +4192,7 @@
         <v>135504219</v>
       </c>
       <c r="B34" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5171,7 +5171,7 @@
         <v>135504198</v>
       </c>
       <c r="B43" t="n">
-        <v>93329</v>
+        <v>93331</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -6602,7 +6602,7 @@
         <v>135504205</v>
       </c>
       <c r="B56" t="n">
-        <v>98142</v>
+        <v>98144</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6714,7 +6714,7 @@
         <v>135504197</v>
       </c>
       <c r="B57" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -8270,7 +8270,7 @@
         <v>135504224</v>
       </c>
       <c r="B71" t="n">
-        <v>93366</v>
+        <v>93368</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>

--- a/artfynd/A 25608-2026 artfynd.xlsx
+++ b/artfynd/A 25608-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135504188</v>
       </c>
       <c r="B2" t="n">
-        <v>83420</v>
+        <v>83422</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>135504199</v>
       </c>
       <c r="B6" t="n">
-        <v>79107</v>
+        <v>79109</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>135504204</v>
       </c>
       <c r="B7" t="n">
-        <v>79107</v>
+        <v>79109</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>135504206</v>
       </c>
       <c r="B9" t="n">
-        <v>92229</v>
+        <v>92243</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>135504226</v>
       </c>
       <c r="B10" t="n">
-        <v>92229</v>
+        <v>92243</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         <v>135504228</v>
       </c>
       <c r="B11" t="n">
-        <v>92229</v>
+        <v>92243</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
         <v>135504177</v>
       </c>
       <c r="B12" t="n">
-        <v>91071</v>
+        <v>91073</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1880,7 +1880,7 @@
         <v>135504187</v>
       </c>
       <c r="B13" t="n">
-        <v>91071</v>
+        <v>91073</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1992,7 +1992,7 @@
         <v>135504207</v>
       </c>
       <c r="B14" t="n">
-        <v>92103</v>
+        <v>92117</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2104,7 +2104,7 @@
         <v>135504220</v>
       </c>
       <c r="B15" t="n">
-        <v>92103</v>
+        <v>92117</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2216,7 +2216,7 @@
         <v>135504222</v>
       </c>
       <c r="B16" t="n">
-        <v>92103</v>
+        <v>92117</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2328,7 +2328,7 @@
         <v>135504232</v>
       </c>
       <c r="B17" t="n">
-        <v>92103</v>
+        <v>92117</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2440,7 +2440,7 @@
         <v>135504223</v>
       </c>
       <c r="B18" t="n">
-        <v>91972</v>
+        <v>91986</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2552,7 +2552,7 @@
         <v>135504227</v>
       </c>
       <c r="B19" t="n">
-        <v>91972</v>
+        <v>91986</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2664,7 +2664,7 @@
         <v>135504229</v>
       </c>
       <c r="B20" t="n">
-        <v>91972</v>
+        <v>91986</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2776,7 +2776,7 @@
         <v>135504236</v>
       </c>
       <c r="B21" t="n">
-        <v>93339</v>
+        <v>93354</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3296,7 +3296,7 @@
         <v>135504181</v>
       </c>
       <c r="B26" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3408,7 +3408,7 @@
         <v>135504182</v>
       </c>
       <c r="B27" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3520,7 +3520,7 @@
         <v>135504184</v>
       </c>
       <c r="B28" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3632,7 +3632,7 @@
         <v>135504185</v>
       </c>
       <c r="B29" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3744,7 +3744,7 @@
         <v>135504191</v>
       </c>
       <c r="B30" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3856,7 +3856,7 @@
         <v>135504194</v>
       </c>
       <c r="B31" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>135504209</v>
       </c>
       <c r="B32" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4080,7 +4080,7 @@
         <v>135504211</v>
       </c>
       <c r="B33" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4192,7 +4192,7 @@
         <v>135504219</v>
       </c>
       <c r="B34" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5171,7 +5171,7 @@
         <v>135504198</v>
       </c>
       <c r="B43" t="n">
-        <v>93331</v>
+        <v>93346</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5487,7 +5487,7 @@
         <v>135504200</v>
       </c>
       <c r="B46" t="n">
-        <v>78844</v>
+        <v>78846</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5710,7 +5710,7 @@
         <v>135504214</v>
       </c>
       <c r="B48" t="n">
-        <v>79198</v>
+        <v>79200</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5822,7 +5822,7 @@
         <v>135504235</v>
       </c>
       <c r="B49" t="n">
-        <v>79198</v>
+        <v>79200</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6138,7 +6138,7 @@
         <v>135504190</v>
       </c>
       <c r="B52" t="n">
-        <v>78445</v>
+        <v>78447</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6250,7 +6250,7 @@
         <v>135504192</v>
       </c>
       <c r="B53" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6375,7 +6375,7 @@
         <v>135504212</v>
       </c>
       <c r="B54" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6492,7 +6492,7 @@
         <v>135524852</v>
       </c>
       <c r="B55" t="n">
-        <v>58141</v>
+        <v>58143</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6602,7 +6602,7 @@
         <v>135504205</v>
       </c>
       <c r="B56" t="n">
-        <v>98144</v>
+        <v>98161</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6714,7 +6714,7 @@
         <v>135504197</v>
       </c>
       <c r="B57" t="n">
-        <v>99298</v>
+        <v>99315</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6928,7 +6928,7 @@
         <v>135504183</v>
       </c>
       <c r="B59" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7040,7 +7040,7 @@
         <v>135504189</v>
       </c>
       <c r="B60" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7152,7 +7152,7 @@
         <v>135504193</v>
       </c>
       <c r="B61" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7264,7 +7264,7 @@
         <v>135504201</v>
       </c>
       <c r="B62" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7376,7 +7376,7 @@
         <v>135504216</v>
       </c>
       <c r="B63" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7488,7 +7488,7 @@
         <v>135504195</v>
       </c>
       <c r="B64" t="n">
-        <v>80031</v>
+        <v>80033</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7600,7 +7600,7 @@
         <v>135504215</v>
       </c>
       <c r="B65" t="n">
-        <v>80031</v>
+        <v>80033</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7712,7 +7712,7 @@
         <v>135504218</v>
       </c>
       <c r="B66" t="n">
-        <v>80031</v>
+        <v>80033</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8046,7 +8046,7 @@
         <v>135504179</v>
       </c>
       <c r="B69" t="n">
-        <v>79464</v>
+        <v>79466</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8158,7 +8158,7 @@
         <v>135504186</v>
       </c>
       <c r="B70" t="n">
-        <v>79464</v>
+        <v>79466</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8270,7 +8270,7 @@
         <v>135504224</v>
       </c>
       <c r="B71" t="n">
-        <v>93368</v>
+        <v>93383</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>

--- a/artfynd/A 25608-2026 artfynd.xlsx
+++ b/artfynd/A 25608-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135504188</v>
       </c>
       <c r="B2" t="n">
-        <v>83422</v>
+        <v>83423</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>135504199</v>
       </c>
       <c r="B6" t="n">
-        <v>79109</v>
+        <v>79110</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>135504204</v>
       </c>
       <c r="B7" t="n">
-        <v>79109</v>
+        <v>79110</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>135504206</v>
       </c>
       <c r="B9" t="n">
-        <v>92243</v>
+        <v>92244</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>135504226</v>
       </c>
       <c r="B10" t="n">
-        <v>92243</v>
+        <v>92244</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         <v>135504228</v>
       </c>
       <c r="B11" t="n">
-        <v>92243</v>
+        <v>92244</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
         <v>135504177</v>
       </c>
       <c r="B12" t="n">
-        <v>91073</v>
+        <v>91074</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1880,7 +1880,7 @@
         <v>135504187</v>
       </c>
       <c r="B13" t="n">
-        <v>91073</v>
+        <v>91074</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1992,7 +1992,7 @@
         <v>135504207</v>
       </c>
       <c r="B14" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2104,7 +2104,7 @@
         <v>135504220</v>
       </c>
       <c r="B15" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2216,7 +2216,7 @@
         <v>135504222</v>
       </c>
       <c r="B16" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2328,7 +2328,7 @@
         <v>135504232</v>
       </c>
       <c r="B17" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2440,7 +2440,7 @@
         <v>135504223</v>
       </c>
       <c r="B18" t="n">
-        <v>91986</v>
+        <v>91987</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2552,7 +2552,7 @@
         <v>135504227</v>
       </c>
       <c r="B19" t="n">
-        <v>91986</v>
+        <v>91987</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2664,7 +2664,7 @@
         <v>135504229</v>
       </c>
       <c r="B20" t="n">
-        <v>91986</v>
+        <v>91987</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2776,7 +2776,7 @@
         <v>135504236</v>
       </c>
       <c r="B21" t="n">
-        <v>93354</v>
+        <v>93355</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3296,7 +3296,7 @@
         <v>135504181</v>
       </c>
       <c r="B26" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3408,7 +3408,7 @@
         <v>135504182</v>
       </c>
       <c r="B27" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3520,7 +3520,7 @@
         <v>135504184</v>
       </c>
       <c r="B28" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3632,7 +3632,7 @@
         <v>135504185</v>
       </c>
       <c r="B29" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3744,7 +3744,7 @@
         <v>135504191</v>
       </c>
       <c r="B30" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3856,7 +3856,7 @@
         <v>135504194</v>
       </c>
       <c r="B31" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>135504209</v>
       </c>
       <c r="B32" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4080,7 +4080,7 @@
         <v>135504211</v>
       </c>
       <c r="B33" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4192,7 +4192,7 @@
         <v>135504219</v>
       </c>
       <c r="B34" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5171,7 +5171,7 @@
         <v>135504198</v>
       </c>
       <c r="B43" t="n">
-        <v>93346</v>
+        <v>93347</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5487,7 +5487,7 @@
         <v>135504200</v>
       </c>
       <c r="B46" t="n">
-        <v>78846</v>
+        <v>78847</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5710,7 +5710,7 @@
         <v>135504214</v>
       </c>
       <c r="B48" t="n">
-        <v>79200</v>
+        <v>79201</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5822,7 +5822,7 @@
         <v>135504235</v>
       </c>
       <c r="B49" t="n">
-        <v>79200</v>
+        <v>79201</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6138,7 +6138,7 @@
         <v>135504190</v>
       </c>
       <c r="B52" t="n">
-        <v>78447</v>
+        <v>78448</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6602,7 +6602,7 @@
         <v>135504205</v>
       </c>
       <c r="B56" t="n">
-        <v>98161</v>
+        <v>98162</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6714,7 +6714,7 @@
         <v>135504197</v>
       </c>
       <c r="B57" t="n">
-        <v>99315</v>
+        <v>99316</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6928,7 +6928,7 @@
         <v>135504183</v>
       </c>
       <c r="B59" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7040,7 +7040,7 @@
         <v>135504189</v>
       </c>
       <c r="B60" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7152,7 +7152,7 @@
         <v>135504193</v>
       </c>
       <c r="B61" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7264,7 +7264,7 @@
         <v>135504201</v>
       </c>
       <c r="B62" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7376,7 +7376,7 @@
         <v>135504216</v>
       </c>
       <c r="B63" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7488,7 +7488,7 @@
         <v>135504195</v>
       </c>
       <c r="B64" t="n">
-        <v>80033</v>
+        <v>80034</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7600,7 +7600,7 @@
         <v>135504215</v>
       </c>
       <c r="B65" t="n">
-        <v>80033</v>
+        <v>80034</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7712,7 +7712,7 @@
         <v>135504218</v>
       </c>
       <c r="B66" t="n">
-        <v>80033</v>
+        <v>80034</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8046,7 +8046,7 @@
         <v>135504179</v>
       </c>
       <c r="B69" t="n">
-        <v>79466</v>
+        <v>79467</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8158,7 +8158,7 @@
         <v>135504186</v>
       </c>
       <c r="B70" t="n">
-        <v>79466</v>
+        <v>79467</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8270,7 +8270,7 @@
         <v>135504224</v>
       </c>
       <c r="B71" t="n">
-        <v>93383</v>
+        <v>93384</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>

--- a/artfynd/A 25608-2026 artfynd.xlsx
+++ b/artfynd/A 25608-2026 artfynd.xlsx
@@ -5171,7 +5171,7 @@
         <v>135504198</v>
       </c>
       <c r="B43" t="n">
-        <v>93347</v>
+        <v>93348</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -8270,7 +8270,7 @@
         <v>135504224</v>
       </c>
       <c r="B71" t="n">
-        <v>93384</v>
+        <v>93385</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>

--- a/artfynd/A 25608-2026 artfynd.xlsx
+++ b/artfynd/A 25608-2026 artfynd.xlsx
@@ -5171,7 +5171,7 @@
         <v>135504198</v>
       </c>
       <c r="B43" t="n">
-        <v>93348</v>
+        <v>93349</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -8270,7 +8270,7 @@
         <v>135504224</v>
       </c>
       <c r="B71" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
